--- a/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_5_3.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_5_3.xlsx
@@ -513,386 +513,386 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_5_3_12</t>
+          <t>model_5_3_24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9948603913898165</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5385431763904708</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9997340004031834</v>
+        <v>0.9591788331561432</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9993553417373522</v>
+        <v>0.9992728802277655</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9994658840220417</v>
+        <v>0.9848700156501718</v>
       </c>
       <c r="G2" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.003051093690536473</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2739407043914549</v>
       </c>
       <c r="I2" t="n">
-        <v>4.967923315861351e-05</v>
+        <v>0.01864488577386567</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0004235253564851686</v>
+        <v>0.0004225624910401599</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002366025619783633</v>
+        <v>0.009533724132452914</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.01094664498806078</v>
       </c>
       <c r="M2" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.0552367060072962</v>
       </c>
       <c r="N2" t="n">
-        <v>1.003060939016538</v>
+        <v>1.123350606644403</v>
       </c>
       <c r="O2" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.05758824693777135</v>
       </c>
       <c r="P2" t="n">
-        <v>68.97712837915313</v>
+        <v>61.5845103311573</v>
       </c>
       <c r="Q2" t="n">
-        <v>99.44902400085815</v>
+        <v>92.05640595286232</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_5_3_22</t>
+          <t>model_5_3_23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9949916925837138</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.537630263224542</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9997340004031834</v>
+        <v>0.9602151777242405</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9993553417373522</v>
+        <v>0.9992967385780966</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9994658840220417</v>
+        <v>0.9852566166093533</v>
       </c>
       <c r="G3" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.00297314762992284</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2744826490825456</v>
       </c>
       <c r="I3" t="n">
-        <v>4.967923315861351e-05</v>
+        <v>0.01817154001752188</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0004235253564851686</v>
+        <v>0.0004086973145822948</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0002366025619783633</v>
+        <v>0.009290118666052088</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.0107513409168353</v>
       </c>
       <c r="M3" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.05452657728046791</v>
       </c>
       <c r="N3" t="n">
-        <v>1.003060939016538</v>
+        <v>1.120199377990869</v>
       </c>
       <c r="O3" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.05684788656087286</v>
       </c>
       <c r="P3" t="n">
-        <v>68.97712837915313</v>
+        <v>61.63626815862557</v>
       </c>
       <c r="Q3" t="n">
-        <v>99.44902400085815</v>
+        <v>92.10816378033059</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_5_3_21</t>
+          <t>model_5_3_22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9952133580235332</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5363114062929997</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9997340004031834</v>
+        <v>0.9619262380882819</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9993553417373522</v>
+        <v>0.9993684173933998</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9994658840220417</v>
+        <v>0.9859098044372944</v>
       </c>
       <c r="G4" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.002841557449397607</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2752655795287621</v>
       </c>
       <c r="I4" t="n">
-        <v>4.967923315861351e-05</v>
+        <v>0.01739002083259093</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0004235253564851686</v>
+        <v>0.0003670414830317384</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0002366025619783633</v>
+        <v>0.008878531157811337</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.01047148995916914</v>
       </c>
       <c r="M4" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.05330626088366738</v>
       </c>
       <c r="N4" t="n">
-        <v>1.003060939016538</v>
+        <v>1.114879407435204</v>
       </c>
       <c r="O4" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.05557561876865734</v>
       </c>
       <c r="P4" t="n">
-        <v>68.97712837915313</v>
+        <v>61.72680595889772</v>
       </c>
       <c r="Q4" t="n">
-        <v>99.44902400085815</v>
+        <v>92.19870158060274</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_5_3_20</t>
+          <t>model_5_3_21</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9952336353305702</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5361470970652082</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9997340004031834</v>
+        <v>0.9620818877234988</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9993553417373522</v>
+        <v>0.9993757900116715</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9994658840220417</v>
+        <v>0.9859696305430955</v>
       </c>
       <c r="G5" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.002829519964006405</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2753631205841681</v>
       </c>
       <c r="I5" t="n">
-        <v>4.967923315861351e-05</v>
+        <v>0.01731892855635924</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0004235253564851686</v>
+        <v>0.0003627569180104332</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0002366025619783633</v>
+        <v>0.008840833459291687</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.01044078357355542</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.05319323231395517</v>
       </c>
       <c r="N5" t="n">
-        <v>1.003060939016538</v>
+        <v>1.114392752066315</v>
       </c>
       <c r="O5" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.05545777833873108</v>
       </c>
       <c r="P5" t="n">
-        <v>68.97712837915313</v>
+        <v>61.73529641148156</v>
       </c>
       <c r="Q5" t="n">
-        <v>99.44902400085815</v>
+        <v>92.20719203318657</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_5_3_19</t>
+          <t>model_5_3_20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9954947518160925</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5350683307201234</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9997340004031834</v>
+        <v>0.9642060049879224</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9993553417373522</v>
+        <v>0.9993746703417313</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9994658840220417</v>
+        <v>0.9867389242864856</v>
       </c>
       <c r="G6" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.002674509938555506</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2760035228868902</v>
       </c>
       <c r="I6" t="n">
-        <v>4.967923315861351e-05</v>
+        <v>0.01634874747562334</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0004235253564851686</v>
+        <v>0.000363407609323122</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002366025619783633</v>
+        <v>0.008356085150455137</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.01025560693690928</v>
       </c>
       <c r="M6" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.05171566434413761</v>
       </c>
       <c r="N6" t="n">
-        <v>1.003060939016538</v>
+        <v>1.10812595641378</v>
       </c>
       <c r="O6" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.05391730724145103</v>
       </c>
       <c r="P6" t="n">
-        <v>68.97712837915313</v>
+        <v>61.84797823191487</v>
       </c>
       <c r="Q6" t="n">
-        <v>99.44902400085815</v>
+        <v>92.31987385361988</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_5_3_18</t>
+          <t>model_5_3_19</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9958735311772015</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5323274724104411</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9997340004031834</v>
+        <v>0.9672279872701293</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9993553417373522</v>
+        <v>0.9994193871753715</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9994658840220417</v>
+        <v>0.9878548041319931</v>
       </c>
       <c r="G7" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.002449650147384811</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2776306147784317</v>
       </c>
       <c r="I7" t="n">
-        <v>4.967923315861351e-05</v>
+        <v>0.01496847055512489</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0004235253564851686</v>
+        <v>0.0003374206160711263</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0002366025619783633</v>
+        <v>0.007652945585598007</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.009764812576106676</v>
       </c>
       <c r="M7" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.04949394051179205</v>
       </c>
       <c r="N7" t="n">
-        <v>1.003060939016538</v>
+        <v>1.099035251747165</v>
       </c>
       <c r="O7" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.05160100002596018</v>
       </c>
       <c r="P7" t="n">
-        <v>68.97712837915313</v>
+        <v>62.02362012321551</v>
       </c>
       <c r="Q7" t="n">
-        <v>99.44902400085815</v>
+        <v>92.49551574492052</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_5_3_17</t>
+          <t>model_5_3_18</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9964345372851338</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5285968989010799</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9997340004031834</v>
+        <v>0.9716311263915151</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9993553417373522</v>
+        <v>0.9995429516623127</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9994658840220417</v>
+        <v>0.989507599701005</v>
       </c>
       <c r="G8" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.002116612687514174</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.279845244365973</v>
       </c>
       <c r="I8" t="n">
-        <v>4.967923315861351e-05</v>
+        <v>0.0129573564123396</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0004235253564851686</v>
+        <v>0.0002656116522666269</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002366025619783633</v>
+        <v>0.006611484032303116</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.009088510408084205</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.04600665916488801</v>
       </c>
       <c r="N8" t="n">
-        <v>1.003060939016538</v>
+        <v>1.08557110515679</v>
       </c>
       <c r="O8" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.04796525789245086</v>
       </c>
       <c r="P8" t="n">
-        <v>68.97712837915313</v>
+        <v>62.31587651406527</v>
       </c>
       <c r="Q8" t="n">
-        <v>99.44902400085815</v>
+        <v>92.78777213577028</v>
       </c>
     </row>
     <row r="9">
@@ -902,52 +902,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9967627450982819</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5263570889034159</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9997340004031834</v>
+        <v>0.9742445907900569</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9993553417373522</v>
+        <v>0.9995853681265086</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9994658840220417</v>
+        <v>0.9904743488862995</v>
       </c>
       <c r="G9" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.001921774351790159</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2811748923353403</v>
       </c>
       <c r="I9" t="n">
-        <v>4.967923315861351e-05</v>
+        <v>0.01176366821201788</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0004235253564851686</v>
+        <v>0.000240961508705481</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0002366025619783633</v>
+        <v>0.006002314860361679</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.008679968838265053</v>
       </c>
       <c r="M9" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.04383804685190889</v>
       </c>
       <c r="N9" t="n">
-        <v>1.003060939016538</v>
+        <v>1.077694117641235</v>
       </c>
       <c r="O9" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.04570432326366186</v>
       </c>
       <c r="P9" t="n">
-        <v>68.97712837915313</v>
+        <v>62.50901275628196</v>
       </c>
       <c r="Q9" t="n">
-        <v>99.44902400085815</v>
+        <v>92.98090837798698</v>
       </c>
     </row>
     <row r="10">
@@ -957,437 +957,437 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9967556887525407</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5262147306056828</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9997340004031834</v>
+        <v>0.9742003435145083</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9993553417373522</v>
+        <v>0.9995751105239116</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9994658840220417</v>
+        <v>0.9904535823210048</v>
       </c>
       <c r="G10" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.001925963303440355</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2812594023704329</v>
       </c>
       <c r="I10" t="n">
-        <v>4.967923315861351e-05</v>
+        <v>0.0117838779576521</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0004235253564851686</v>
+        <v>0.0002469226698112267</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0002366025619783633</v>
+        <v>0.006015400313731663</v>
       </c>
       <c r="L10" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.008779366732826</v>
       </c>
       <c r="M10" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.04388579842546282</v>
       </c>
       <c r="N10" t="n">
-        <v>1.003060939016538</v>
+        <v>1.077863469939023</v>
       </c>
       <c r="O10" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.04575410772056138</v>
       </c>
       <c r="P10" t="n">
-        <v>68.97712837915313</v>
+        <v>62.50465803807559</v>
       </c>
       <c r="Q10" t="n">
-        <v>99.44902400085815</v>
+        <v>92.97655365978061</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_5_3_14</t>
+          <t>model_5_3_17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9967942900387318</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5261276067985561</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9997340004031834</v>
+        <v>0.9744851325657684</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9993553417373522</v>
+        <v>0.9995973040678268</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9994658840220417</v>
+        <v>0.9905670317701388</v>
       </c>
       <c r="G11" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.001903047912468643</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2813111228258959</v>
       </c>
       <c r="I11" t="n">
-        <v>4.967923315861351e-05</v>
+        <v>0.01165380182948307</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0004235253564851686</v>
+        <v>0.0002340249883563857</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0002366025619783633</v>
+        <v>0.00594391340891973</v>
       </c>
       <c r="L11" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.008641240066612372</v>
       </c>
       <c r="M11" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.04362393737924906</v>
       </c>
       <c r="N11" t="n">
-        <v>1.003060939016538</v>
+        <v>1.076937039070438</v>
       </c>
       <c r="O11" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.04548109870748319</v>
       </c>
       <c r="P11" t="n">
-        <v>68.97712837915313</v>
+        <v>62.52859702729999</v>
       </c>
       <c r="Q11" t="n">
-        <v>99.44902400085815</v>
+        <v>93.00049264900501</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_5_3_13</t>
+          <t>model_5_3_14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9971024663936875</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5233424741210093</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9997340004031834</v>
+        <v>0.9770176890326295</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9993553417373522</v>
+        <v>0.9995791575987869</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9994658840220417</v>
+        <v>0.9914765416305849</v>
       </c>
       <c r="G12" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.001720101115641571</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2829644978947548</v>
       </c>
       <c r="I12" t="n">
-        <v>4.967923315861351e-05</v>
+        <v>0.01049706796586995</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0004235253564851686</v>
+        <v>0.0002445707298612551</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0002366025619783633</v>
+        <v>0.005370811949939264</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.008553789311520794</v>
       </c>
       <c r="M12" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.04147410174604835</v>
       </c>
       <c r="N12" t="n">
-        <v>1.003060939016538</v>
+        <v>1.0695408065515</v>
       </c>
       <c r="O12" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.04323974012060387</v>
       </c>
       <c r="P12" t="n">
-        <v>68.97712837915313</v>
+        <v>62.73074440344205</v>
       </c>
       <c r="Q12" t="n">
-        <v>99.44902400085815</v>
+        <v>93.20264002514708</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_5_3_23</t>
+          <t>model_5_3_13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9973529358791835</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.52193718990393</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9997340004031834</v>
+        <v>0.9790193353921917</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9993553417373522</v>
+        <v>0.9996075576463429</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9994658840220417</v>
+        <v>0.9922150763652278</v>
       </c>
       <c r="G13" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.001571411609332729</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2837987353111304</v>
       </c>
       <c r="I13" t="n">
-        <v>4.967923315861351e-05</v>
+        <v>0.009582824924350289</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0004235253564851686</v>
+        <v>0.0002280661658276696</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0002366025619783633</v>
+        <v>0.00490544554508898</v>
       </c>
       <c r="L13" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.007969177526216911</v>
       </c>
       <c r="M13" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.03964103441300099</v>
       </c>
       <c r="N13" t="n">
-        <v>1.003060939016538</v>
+        <v>1.063529538899596</v>
       </c>
       <c r="O13" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.04132863531621619</v>
       </c>
       <c r="P13" t="n">
-        <v>68.97712837915313</v>
+        <v>62.91156189871666</v>
       </c>
       <c r="Q13" t="n">
-        <v>99.44902400085815</v>
+        <v>93.38345752042167</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>model_5_3_24</t>
+          <t>model_5_3_12</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9975557080038653</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5212030858498975</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9997340004031834</v>
+        <v>0.9806233358382959</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9993553417373522</v>
+        <v>0.999641640681148</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9994658840220417</v>
+        <v>0.9928121259755041</v>
       </c>
       <c r="G14" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.001451037316821903</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.284234531189248</v>
       </c>
       <c r="I14" t="n">
-        <v>4.967923315861351e-05</v>
+        <v>0.00885020487913608</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0004235253564851686</v>
+        <v>0.0002082589584879466</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0002366025619783633</v>
+        <v>0.004529231918812013</v>
       </c>
       <c r="L14" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.007540621588772404</v>
       </c>
       <c r="M14" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.03809248373133345</v>
       </c>
       <c r="N14" t="n">
-        <v>1.003060939016538</v>
+        <v>1.058663007907233</v>
       </c>
       <c r="O14" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.03971415962608824</v>
       </c>
       <c r="P14" t="n">
-        <v>68.97712837915313</v>
+        <v>63.0709531748162</v>
       </c>
       <c r="Q14" t="n">
-        <v>99.44902400085815</v>
+        <v>93.54284879652121</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_5_3_10</t>
+          <t>model_5_3_11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9976078124940282</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5210178636962468</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9997340004031834</v>
+        <v>0.9810626652079937</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9993553417373522</v>
+        <v>0.9996294980831579</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9994658840220417</v>
+        <v>0.9929657512670399</v>
       </c>
       <c r="G15" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.001420105840664447</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2843444870608355</v>
       </c>
       <c r="I15" t="n">
-        <v>4.967923315861351e-05</v>
+        <v>0.00864954315022342</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0004235253564851686</v>
+        <v>0.0002153155764624623</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0002366025619783633</v>
+        <v>0.004432429363342941</v>
       </c>
       <c r="L15" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.007419029948316039</v>
       </c>
       <c r="M15" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.03768429169646746</v>
       </c>
       <c r="N15" t="n">
-        <v>1.003060939016538</v>
+        <v>1.057412500143323</v>
       </c>
       <c r="O15" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.03928859001122401</v>
       </c>
       <c r="P15" t="n">
-        <v>68.97712837915313</v>
+        <v>63.11404774893485</v>
       </c>
       <c r="Q15" t="n">
-        <v>99.44902400085815</v>
+        <v>93.58594337063987</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_5_3_9</t>
+          <t>model_5_3_10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9978638692858244</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5184234866393764</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9997340004031834</v>
+        <v>0.9831122582549032</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9993553417373522</v>
+        <v>0.9996631766479198</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9994658840220417</v>
+        <v>0.9937241090277874</v>
       </c>
       <c r="G16" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.001268099467976764</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2858846213530471</v>
       </c>
       <c r="I16" t="n">
-        <v>4.967923315861351e-05</v>
+        <v>0.007713400673240616</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0004235253564851686</v>
+        <v>0.0001957434251280119</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0002366025619783633</v>
+        <v>0.003954572049184313</v>
       </c>
       <c r="L16" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.007397772109151917</v>
       </c>
       <c r="M16" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.0356103842716807</v>
       </c>
       <c r="N16" t="n">
-        <v>1.003060939016538</v>
+        <v>1.051267137140215</v>
       </c>
       <c r="O16" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.03712639205378386</v>
       </c>
       <c r="P16" t="n">
-        <v>68.97712837915313</v>
+        <v>63.34047196253421</v>
       </c>
       <c r="Q16" t="n">
-        <v>99.44902400085815</v>
+        <v>93.81236758423923</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_5_3_8</t>
+          <t>model_5_3_9</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9981980101278621</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5158643014464176</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9997340004031834</v>
+        <v>0.9858062743658788</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9993553417373522</v>
+        <v>0.9996936804275753</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9994658840220417</v>
+        <v>0.9947145477889865</v>
       </c>
       <c r="G17" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.001069739030010324</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2874038642346315</v>
       </c>
       <c r="I17" t="n">
-        <v>4.967923315861351e-05</v>
+        <v>0.006482920837761534</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0004235253564851686</v>
+        <v>0.00017801628634075</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0002366025619783633</v>
+        <v>0.003330475572873799</v>
       </c>
       <c r="L17" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.007077697740040582</v>
       </c>
       <c r="M17" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.03270686518164533</v>
       </c>
       <c r="N17" t="n">
-        <v>1.003060939016538</v>
+        <v>1.043247756931309</v>
       </c>
       <c r="O17" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.03409926414497258</v>
       </c>
       <c r="P17" t="n">
-        <v>68.97712837915313</v>
+        <v>63.68068111488538</v>
       </c>
       <c r="Q17" t="n">
-        <v>99.44902400085815</v>
+        <v>94.1525767365904</v>
       </c>
     </row>
     <row r="18">
@@ -1397,52 +1397,52 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9985851056529526</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5126490926854936</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9997340004031834</v>
+        <v>0.9890264167551426</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9993553417373522</v>
+        <v>0.9998791475954431</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9994658840220417</v>
+        <v>0.9959671505300755</v>
       </c>
       <c r="G18" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0008399424046606974</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2893125510449026</v>
       </c>
       <c r="I18" t="n">
-        <v>4.967923315861351e-05</v>
+        <v>0.005012135172739751</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0004235253564851686</v>
+        <v>7.023284893058203e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0002366025619783633</v>
+        <v>0.002541184010835167</v>
       </c>
       <c r="L18" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.007870336531006826</v>
       </c>
       <c r="M18" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.0289817598613455</v>
       </c>
       <c r="N18" t="n">
-        <v>1.003060939016538</v>
+        <v>1.033957464329139</v>
       </c>
       <c r="O18" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.03021557337915653</v>
       </c>
       <c r="P18" t="n">
-        <v>68.97712837915313</v>
+        <v>64.16435446871557</v>
       </c>
       <c r="Q18" t="n">
-        <v>99.44902400085815</v>
+        <v>94.63625009042059</v>
       </c>
     </row>
     <row r="19">
@@ -1452,382 +1452,382 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9988456702680281</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.510849675771284</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9997340004031834</v>
+        <v>0.9911452748221382</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9993553417373522</v>
+        <v>0.9999141653100234</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9994658840220417</v>
+        <v>0.9967512293180467</v>
       </c>
       <c r="G19" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0006852599933465818</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2903807626559407</v>
       </c>
       <c r="I19" t="n">
-        <v>4.967923315861351e-05</v>
+        <v>0.00404435620695762</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0004235253564851686</v>
+        <v>4.988245650739776e-05</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0002366025619783633</v>
+        <v>0.002047119331732509</v>
       </c>
       <c r="L19" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.007581189456762572</v>
       </c>
       <c r="M19" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.02617747110296527</v>
       </c>
       <c r="N19" t="n">
-        <v>1.003060939016538</v>
+        <v>1.027703913567326</v>
       </c>
       <c r="O19" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.02729190024265405</v>
       </c>
       <c r="P19" t="n">
-        <v>68.97712837915313</v>
+        <v>64.57142447876608</v>
       </c>
       <c r="Q19" t="n">
-        <v>99.44902400085815</v>
+        <v>95.04332010047109</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_5_3_5</t>
+          <t>model_5_3_8</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9987666257919713</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5089661622632033</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9997340004031834</v>
+        <v>0.9903398225597625</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9993553417373522</v>
+        <v>0.9998036734001031</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9994658840220417</v>
+        <v>0.9964084240548963</v>
       </c>
       <c r="G20" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0007321842088774212</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2914988976378844</v>
       </c>
       <c r="I20" t="n">
-        <v>4.967923315861351e-05</v>
+        <v>0.004412242933119551</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0004235253564851686</v>
+        <v>0.0001140943490711328</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0002366025619783633</v>
+        <v>0.002263128200906709</v>
       </c>
       <c r="L20" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.006070342992485885</v>
       </c>
       <c r="M20" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.02705890258080363</v>
       </c>
       <c r="N20" t="n">
-        <v>1.003060939016538</v>
+        <v>1.029600980992689</v>
       </c>
       <c r="O20" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.02821085608331868</v>
       </c>
       <c r="P20" t="n">
-        <v>68.97712837915313</v>
+        <v>64.43895684837999</v>
       </c>
       <c r="Q20" t="n">
-        <v>99.44902400085815</v>
+        <v>94.910852470085</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_5_3_4</t>
+          <t>model_5_3_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9992076056130129</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.504440533107974</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9997340004031834</v>
+        <v>0.9949061503117507</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9993553417373522</v>
+        <v>0.999951335080449</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9994658840220417</v>
+        <v>0.998131411497482</v>
       </c>
       <c r="G21" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.000470399537770761</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2941855066014287</v>
       </c>
       <c r="I21" t="n">
-        <v>4.967923315861351e-05</v>
+        <v>0.002326593111606336</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0004235253564851686</v>
+        <v>2.828140619608907e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0002366025619783633</v>
+        <v>0.001177437258901213</v>
       </c>
       <c r="L21" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.009254813771904973</v>
       </c>
       <c r="M21" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.02168869608276996</v>
       </c>
       <c r="N21" t="n">
-        <v>1.003060939016538</v>
+        <v>1.01901746528769</v>
       </c>
       <c r="O21" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.02261202877680376</v>
       </c>
       <c r="P21" t="n">
-        <v>68.97712837915313</v>
+        <v>65.32385628802105</v>
       </c>
       <c r="Q21" t="n">
-        <v>99.44902400085815</v>
+        <v>95.79575190972606</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_5_3_3</t>
+          <t>model_5_3_4</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9991843869112084</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5016056516892711</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9997340004031834</v>
+        <v>0.9972657821518002</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9993553417373522</v>
+        <v>0.9997550746505364</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9994658840220417</v>
+        <v>0.998896101999358</v>
       </c>
       <c r="G22" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0004841831621575981</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2958684146720716</v>
       </c>
       <c r="I22" t="n">
-        <v>4.967923315861351e-05</v>
+        <v>0.001248841799538689</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0004235253564851686</v>
+        <v>0.0001423373008688624</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0002366025619783633</v>
+        <v>0.000695589550203776</v>
       </c>
       <c r="L22" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.01220543343988692</v>
       </c>
       <c r="M22" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.02200416238254931</v>
       </c>
       <c r="N22" t="n">
-        <v>1.003060939016538</v>
+        <v>1.019574714130999</v>
       </c>
       <c r="O22" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.02294092513006998</v>
       </c>
       <c r="P22" t="n">
-        <v>68.97712837915313</v>
+        <v>65.26609457725179</v>
       </c>
       <c r="Q22" t="n">
-        <v>99.44902400085815</v>
+        <v>95.73799019895681</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_5_3_2</t>
+          <t>model_5_3_3</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9992165193461173</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.4998888126351819</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9997340004031834</v>
+        <v>0.9981482455931937</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9993553417373522</v>
+        <v>0.9997332023719584</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9994658840220417</v>
+        <v>0.9992058421987189</v>
       </c>
       <c r="G23" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0004651079607467471</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2968876044981644</v>
       </c>
       <c r="I23" t="n">
-        <v>4.967923315861351e-05</v>
+        <v>0.0008457805610559591</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0004235253564851686</v>
+        <v>0.0001550482803711957</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0002366025619783633</v>
+        <v>0.0005004156792228067</v>
       </c>
       <c r="L23" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.01269527379603431</v>
       </c>
       <c r="M23" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.02156636178743988</v>
       </c>
       <c r="N23" t="n">
-        <v>1.003060939016538</v>
+        <v>1.018803535693184</v>
       </c>
       <c r="O23" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.02248448645725457</v>
       </c>
       <c r="P23" t="n">
-        <v>68.97712837915313</v>
+        <v>65.34648201135226</v>
       </c>
       <c r="Q23" t="n">
-        <v>99.44902400085815</v>
+        <v>95.81837763305728</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_5_3_1</t>
+          <t>model_5_3_2</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9992386167703513</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.4929616425409949</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9997340004031834</v>
+        <v>0.9998252043836899</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9993553417373522</v>
+        <v>0.9993868711276016</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9994658840220417</v>
+        <v>0.9996539123882217</v>
       </c>
       <c r="G24" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0004519899751624518</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.3009998719042408</v>
       </c>
       <c r="I24" t="n">
-        <v>4.967923315861351e-05</v>
+        <v>7.983711764875977e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0004235253564851686</v>
+        <v>0.0003563171757152401</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0002366025619783633</v>
+        <v>0.000218077146682</v>
       </c>
       <c r="L24" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.009529502249512661</v>
       </c>
       <c r="M24" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.02126005585981494</v>
       </c>
       <c r="N24" t="n">
-        <v>1.003060939016538</v>
+        <v>1.018273197511569</v>
       </c>
       <c r="O24" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.02216514045214996</v>
       </c>
       <c r="P24" t="n">
-        <v>68.97712837915313</v>
+        <v>65.40370111444426</v>
       </c>
       <c r="Q24" t="n">
-        <v>99.44902400085815</v>
+        <v>95.87559673614928</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_5_3_11</t>
+          <t>model_5_3_1</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9990916177603969</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.491991410861401</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9997340004031834</v>
+        <v>0.9998282643815138</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9993553417373522</v>
+        <v>0.9992482448290048</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9994658840220417</v>
+        <v>0.9995910955620536</v>
       </c>
       <c r="G25" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0005392549374979579</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.301575843341074</v>
       </c>
       <c r="I25" t="n">
-        <v>4.967923315861351e-05</v>
+        <v>7.843947729927554e-05</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0004235253564851686</v>
+        <v>0.0004368792458110187</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0002366025619783633</v>
+        <v>0.0002576593615551471</v>
       </c>
       <c r="L25" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.01041150250231943</v>
       </c>
       <c r="M25" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.02322186335111715</v>
       </c>
       <c r="N25" t="n">
-        <v>1.003060939016538</v>
+        <v>1.021801173750474</v>
       </c>
       <c r="O25" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.02421046614985826</v>
       </c>
       <c r="P25" t="n">
-        <v>68.97712837915313</v>
+        <v>65.0506442330104</v>
       </c>
       <c r="Q25" t="n">
-        <v>99.44902400085815</v>
+        <v>95.52253985471542</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9997150092261247</v>
+        <v>0.9989442804620136</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3978572598893595</v>
+        <v>0.4881283053245761</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9990487404702986</v>
+        <v>0.9993156405526462</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9995960988654343</v>
+        <v>0.999102387390265</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9994999603158995</v>
+        <v>0.9993380465821202</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0001691828343327821</v>
+        <v>0.0006267207224582214</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3574579417416667</v>
+        <v>0.3038691496652033</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0001776613368439591</v>
+        <v>0.0003125781233296061</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0002653535708967536</v>
+        <v>0.000521643661529204</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0002215074538703563</v>
+        <v>0.000417110892429405</v>
       </c>
       <c r="L26" t="n">
-        <v>0.006841257505214519</v>
+        <v>0.01104906540572233</v>
       </c>
       <c r="M26" t="n">
-        <v>0.01300703018881643</v>
+        <v>0.02503439079462932</v>
       </c>
       <c r="N26" t="n">
-        <v>1.006839778573008</v>
+        <v>1.025337268911675</v>
       </c>
       <c r="O26" t="n">
-        <v>0.01356076639221871</v>
+        <v>0.0261001566390898</v>
       </c>
       <c r="P26" t="n">
-        <v>67.36906113574531</v>
+        <v>64.75001907057332</v>
       </c>
       <c r="Q26" t="n">
-        <v>97.84095675745033</v>
+        <v>95.22191469227833</v>
       </c>
     </row>
   </sheetData>
